--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_h_9.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_h_9.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.02873976437782484</v>
+        <v>0.02400041470779345</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008444211796812763</v>
+        <v>0.008438734620987253</v>
       </c>
       <c r="C2" t="n">
-        <v>57267729</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>57267729</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>38985638</v>
+        <v>4074884</v>
       </c>
       <c r="L2" t="n">
-        <v>20562642</v>
+        <v>1858433</v>
       </c>
       <c r="M2" t="n">
-        <v>4760672</v>
+        <v>351067</v>
       </c>
       <c r="N2" t="n">
-        <v>217875</v>
+        <v>8488</v>
       </c>
       <c r="O2" t="n">
-        <v>2859112</v>
+        <v>204543</v>
       </c>
       <c r="P2" t="n">
-        <v>1141871</v>
+        <v>75884</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.999987781047821</v>
+        <v>0.9999836087226868</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8345626592636108</v>
+        <v>0.7548642158508301</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6911917924880981</v>
+        <v>0.5708549022674561</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6135153770446777</v>
+        <v>0.4606579840183258</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2420064359903336</v>
+        <v>0.06318296492099762</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6715902090072632</v>
+        <v>0.5078646540641785</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7695606350898743</v>
+        <v>0.650627613067627</v>
       </c>
       <c r="X2" t="n">
-        <v>57267729</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>57267729</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>43599582</v>
+        <v>4801660</v>
       </c>
       <c r="AG2" t="n">
-        <v>27067956</v>
+        <v>3018155</v>
       </c>
       <c r="AH2" t="n">
-        <v>7231912</v>
+        <v>805700</v>
       </c>
       <c r="AI2" t="n">
-        <v>533313</v>
+        <v>59334</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4140105</v>
+        <v>460847</v>
       </c>
       <c r="AK2" t="n">
-        <v>1621484</v>
+        <v>180323</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9560521245002747</v>
+        <v>0.9551666378974915</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9115551710128784</v>
+        <v>0.9119651317596436</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8579047322273254</v>
+        <v>0.8582442998886108</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6615177989006042</v>
+        <v>0.660926342010498</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019250869750977</v>
+        <v>0.9019715189933777</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314548373222351</v>
+        <v>0.9314685463905334</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.007412657221841805</v>
+        <v>0.006048568139975822</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002022735960981907</v>
+        <v>0.002022102987121896</v>
       </c>
       <c r="C3" t="n">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="D3" t="n">
-        <v>38985638</v>
+        <v>4074884</v>
       </c>
       <c r="E3" t="n">
-        <v>6306934</v>
+        <v>904056</v>
       </c>
       <c r="F3" t="n">
-        <v>202195</v>
+        <v>31171</v>
       </c>
       <c r="G3" t="n">
-        <v>25033</v>
+        <v>2820</v>
       </c>
       <c r="H3" t="n">
-        <v>13219</v>
+        <v>2103</v>
       </c>
       <c r="I3" t="n">
-        <v>996</v>
+        <v>164</v>
       </c>
       <c r="J3" t="n">
-        <v>90864371</v>
+        <v>10069516</v>
       </c>
       <c r="K3" t="n">
-        <v>94870499</v>
+        <v>10077490</v>
       </c>
       <c r="L3" t="n">
-        <v>109195141</v>
+        <v>11700113</v>
       </c>
       <c r="M3" t="n">
-        <v>136695101</v>
+        <v>15064332</v>
       </c>
       <c r="N3" t="n">
-        <v>146643428</v>
+        <v>16200271</v>
       </c>
       <c r="O3" t="n">
-        <v>142141474</v>
+        <v>15706391</v>
       </c>
       <c r="P3" t="n">
-        <v>146049525</v>
+        <v>16181566</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8561857938766479</v>
+        <v>0.8125025629997253</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6911637187004089</v>
+        <v>0.5599724054336548</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5641469359397888</v>
+        <v>0.3732230067253113</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2699944674968719</v>
+        <v>0.09444017708301544</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6224647760391235</v>
+        <v>0.3999659717082977</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6557389497756958</v>
+        <v>0.3917887806892395</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>43599582</v>
+        <v>4801660</v>
       </c>
       <c r="Z3" t="n">
-        <v>1794818</v>
+        <v>198183</v>
       </c>
       <c r="AA3" t="n">
-        <v>77289</v>
+        <v>8469</v>
       </c>
       <c r="AB3" t="n">
-        <v>61790</v>
+        <v>6873</v>
       </c>
       <c r="AC3" t="n">
-        <v>337</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>270</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>90865071</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>100594524</v>
+        <v>11175395</v>
       </c>
       <c r="AG3" t="n">
-        <v>115755743</v>
+        <v>12805854</v>
       </c>
       <c r="AH3" t="n">
-        <v>138496265</v>
+        <v>15342287</v>
       </c>
       <c r="AI3" t="n">
-        <v>147052956</v>
+        <v>16295683</v>
       </c>
       <c r="AJ3" t="n">
-        <v>143089396</v>
+        <v>15854513</v>
       </c>
       <c r="AK3" t="n">
-        <v>146272126</v>
+        <v>16209047</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575152397155762</v>
+        <v>0.9574164748191833</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9098241925239563</v>
+        <v>0.9094131588935852</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8569927215576172</v>
+        <v>0.8565481305122375</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6608906984329224</v>
+        <v>0.6601688861846924</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.901353120803833</v>
+        <v>0.9011460542678833</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311649203300476</v>
+        <v>0.931006908416748</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.06642101065551609</v>
+        <v>0.05720150111717914</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03194306376401414</v>
+        <v>0.03192845045564235</v>
       </c>
       <c r="C4" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>7186767</v>
+        <v>1210909</v>
       </c>
       <c r="E4" t="n">
-        <v>20562642</v>
+        <v>1858433</v>
       </c>
       <c r="F4" t="n">
-        <v>1685768</v>
+        <v>198731</v>
       </c>
       <c r="G4" t="n">
-        <v>108816</v>
+        <v>19031</v>
       </c>
       <c r="H4" t="n">
-        <v>186221</v>
+        <v>28420</v>
       </c>
       <c r="I4" t="n">
-        <v>20496</v>
+        <v>3262</v>
       </c>
       <c r="J4" t="n">
-        <v>700</v>
+        <v>104</v>
       </c>
       <c r="K4" t="n">
-        <v>7728215</v>
+        <v>1323284</v>
       </c>
       <c r="L4" t="n">
-        <v>9186905</v>
+        <v>1397093</v>
       </c>
       <c r="M4" t="n">
-        <v>2998990</v>
+        <v>411032</v>
       </c>
       <c r="N4" t="n">
-        <v>682411</v>
+        <v>125852</v>
       </c>
       <c r="O4" t="n">
-        <v>1398115</v>
+        <v>198208</v>
       </c>
       <c r="P4" t="n">
-        <v>341925</v>
+        <v>40748</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999938607215881</v>
+        <v>0.9999918341636658</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8452360033988953</v>
+        <v>0.7826235890388489</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6911777853965759</v>
+        <v>0.5653612613677979</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5877963304519653</v>
+        <v>0.4123565554618835</v>
       </c>
       <c r="U4" t="n">
-        <v>0.255235493183136</v>
+        <v>0.07571236044168472</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6460950374603271</v>
+        <v>0.4475032687187195</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7081049680709839</v>
+        <v>0.4890725314617157</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1871575</v>
+        <v>210622</v>
       </c>
       <c r="Z4" t="n">
-        <v>27067956</v>
+        <v>3018155</v>
       </c>
       <c r="AA4" t="n">
-        <v>750277</v>
+        <v>83217</v>
       </c>
       <c r="AB4" t="n">
-        <v>50035</v>
+        <v>5601</v>
       </c>
       <c r="AC4" t="n">
-        <v>10299</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>612</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2004190</v>
+        <v>225379</v>
       </c>
       <c r="AG4" t="n">
-        <v>2626303</v>
+        <v>291352</v>
       </c>
       <c r="AH4" t="n">
-        <v>1197826</v>
+        <v>133077</v>
       </c>
       <c r="AI4" t="n">
-        <v>272883</v>
+        <v>30440</v>
       </c>
       <c r="AJ4" t="n">
-        <v>450193</v>
+        <v>50086</v>
       </c>
       <c r="AK4" t="n">
-        <v>119324</v>
+        <v>13267</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567831754684448</v>
+        <v>0.9562901854515076</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106888175010681</v>
+        <v>0.9106873869895935</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8574485182762146</v>
+        <v>0.857395350933075</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6612040996551514</v>
+        <v>0.6605474352836609</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016390442848206</v>
+        <v>0.9015586376190186</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313098192214966</v>
+        <v>0.9312376976013184</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>383114</v>
+        <v>83249</v>
       </c>
       <c r="E5" t="n">
-        <v>2355533</v>
+        <v>386132</v>
       </c>
       <c r="F5" t="n">
-        <v>4760672</v>
+        <v>351067</v>
       </c>
       <c r="G5" t="n">
-        <v>228678</v>
+        <v>35710</v>
       </c>
       <c r="H5" t="n">
-        <v>638955</v>
+        <v>73744</v>
       </c>
       <c r="I5" t="n">
-        <v>71674</v>
+        <v>10714</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6548448</v>
+        <v>940342</v>
       </c>
       <c r="L5" t="n">
-        <v>9188112</v>
+        <v>1460361</v>
       </c>
       <c r="M5" t="n">
-        <v>3678037</v>
+        <v>589569</v>
       </c>
       <c r="N5" t="n">
-        <v>589086</v>
+        <v>81389</v>
       </c>
       <c r="O5" t="n">
-        <v>1734099</v>
+        <v>306858</v>
       </c>
       <c r="P5" t="n">
-        <v>599479</v>
+        <v>117802</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999952912330627</v>
+        <v>0.9999936819076538</v>
       </c>
       <c r="R5" t="n">
-        <v>0.903622567653656</v>
+        <v>0.8621085286140442</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8759557604789734</v>
+        <v>0.8259348273277283</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9549254179000854</v>
+        <v>0.9390472173690796</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9914165139198303</v>
+        <v>0.9873756766319275</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9788553714752197</v>
+        <v>0.9692333340644836</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9936448931694031</v>
+        <v>0.9903417229652405</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>73158</v>
+        <v>8120</v>
       </c>
       <c r="Z5" t="n">
-        <v>774906</v>
+        <v>86892</v>
       </c>
       <c r="AA5" t="n">
-        <v>7231912</v>
+        <v>805700</v>
       </c>
       <c r="AB5" t="n">
-        <v>90018</v>
+        <v>10028</v>
       </c>
       <c r="AC5" t="n">
-        <v>263018</v>
+        <v>29263</v>
       </c>
       <c r="AD5" t="n">
-        <v>5697</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1934504</v>
+        <v>213566</v>
       </c>
       <c r="AG5" t="n">
-        <v>2682798</v>
+        <v>300639</v>
       </c>
       <c r="AH5" t="n">
-        <v>1206797</v>
+        <v>134936</v>
       </c>
       <c r="AI5" t="n">
-        <v>273648</v>
+        <v>30543</v>
       </c>
       <c r="AJ5" t="n">
-        <v>453106</v>
+        <v>50554</v>
       </c>
       <c r="AK5" t="n">
-        <v>119866</v>
+        <v>13363</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734110832214355</v>
+        <v>0.9732611179351807</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641598463058472</v>
+        <v>0.9639381766319275</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837670922279358</v>
+        <v>0.9836736917495728</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963105320930481</v>
+        <v>0.9962851405143738</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939020872116089</v>
+        <v>0.993869423866272</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983853101730347</v>
+        <v>0.998377799987793</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>115</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>126867</v>
+        <v>20045</v>
       </c>
       <c r="E6" t="n">
-        <v>169589</v>
+        <v>25284</v>
       </c>
       <c r="F6" t="n">
-        <v>191489</v>
+        <v>26280</v>
       </c>
       <c r="G6" t="n">
-        <v>217875</v>
+        <v>8488</v>
       </c>
       <c r="H6" t="n">
-        <v>89862</v>
+        <v>8545</v>
       </c>
       <c r="I6" t="n">
-        <v>11164</v>
+        <v>1210</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>58973</v>
+        <v>6601</v>
       </c>
       <c r="Z6" t="n">
-        <v>48553</v>
+        <v>5386</v>
       </c>
       <c r="AA6" t="n">
-        <v>98760</v>
+        <v>11048</v>
       </c>
       <c r="AB6" t="n">
-        <v>533313</v>
+        <v>59334</v>
       </c>
       <c r="AC6" t="n">
-        <v>63033</v>
+        <v>7027</v>
       </c>
       <c r="AD6" t="n">
-        <v>4329</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>165</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>30198</v>
+        <v>8792</v>
       </c>
       <c r="E7" t="n">
-        <v>325091</v>
+        <v>73877</v>
       </c>
       <c r="F7" t="n">
-        <v>853676</v>
+        <v>139656</v>
       </c>
       <c r="G7" t="n">
-        <v>287374</v>
+        <v>59123</v>
       </c>
       <c r="H7" t="n">
-        <v>2859112</v>
+        <v>204543</v>
       </c>
       <c r="I7" t="n">
-        <v>237595</v>
+        <v>25398</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>232</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>7297</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>268516</v>
+        <v>30010</v>
       </c>
       <c r="AB7" t="n">
-        <v>68645</v>
+        <v>7671</v>
       </c>
       <c r="AC7" t="n">
-        <v>4140105</v>
+        <v>460847</v>
       </c>
       <c r="AD7" t="n">
-        <v>108416</v>
+        <v>12055</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>1269</v>
+        <v>289</v>
       </c>
       <c r="E8" t="n">
-        <v>29758</v>
+        <v>7744</v>
       </c>
       <c r="F8" t="n">
-        <v>65862</v>
+        <v>15194</v>
       </c>
       <c r="G8" t="n">
-        <v>32510</v>
+        <v>9168</v>
       </c>
       <c r="H8" t="n">
-        <v>469858</v>
+        <v>85396</v>
       </c>
       <c r="I8" t="n">
-        <v>1141871</v>
+        <v>75884</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>252</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>729</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2984</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2395</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>113506</v>
+        <v>12654</v>
       </c>
       <c r="AD8" t="n">
-        <v>1621484</v>
+        <v>180323</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
